--- a/계명대학교-24학년도-정시.xlsx
+++ b/계명대학교-24학년도-정시.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\findmyuniv data\findmyuniv_data_cleaning\"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2231" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="462">
   <si>
     <t>비교대학 추가</t>
   </si>
@@ -1486,12 +1486,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1523,16 +1529,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1835,6 +1841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1856,6 +1863,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -2701,6 +2709,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:DC73"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -2770,364 +2779,364 @@
     <col min="107" max="107" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:107" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:107" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CH1" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CM1" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CN1" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CO1" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CP1" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CR1" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CS1" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CT1" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CU1" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CV1" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CW1" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CX1" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CY1" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="CZ1" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DA1" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DB1" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DC1" s="3" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="2" spans="1:107" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>73</v>
+        <v>333</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>75</v>
+        <v>334</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>76</v>
+        <v>335</v>
       </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>78</v>
+      <c r="J2" s="4">
+        <v>330.84</v>
+      </c>
+      <c r="K2" s="4">
+        <v>410</v>
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4" t="s">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
@@ -3251,11 +3260,15 @@
       <c r="CI2" s="4"/>
       <c r="CJ2" s="4"/>
       <c r="CK2" s="4"/>
-      <c r="CL2" s="4"/>
+      <c r="CL2" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM2" s="4"/>
       <c r="CN2" s="4"/>
       <c r="CO2" s="4"/>
-      <c r="CP2" s="4"/>
+      <c r="CP2" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ2" s="4"/>
       <c r="CR2" s="4"/>
       <c r="CS2" s="4"/>
@@ -3278,33 +3291,33 @@
         <v>456</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>83</v>
       </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>78</v>
+      <c r="J3" s="4">
+        <v>275.32</v>
+      </c>
+      <c r="K3" s="4">
+        <v>410</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4" t="s">
-        <v>85</v>
+        <v>301</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -3428,11 +3441,15 @@
       <c r="CI3" s="4"/>
       <c r="CJ3" s="4"/>
       <c r="CK3" s="4"/>
-      <c r="CL3" s="4"/>
+      <c r="CL3" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM3" s="4"/>
       <c r="CN3" s="4"/>
       <c r="CO3" s="4"/>
-      <c r="CP3" s="4"/>
+      <c r="CP3" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ3" s="4"/>
       <c r="CR3" s="4"/>
       <c r="CS3" s="4"/>
@@ -3461,27 +3478,27 @@
         <v>458</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>78</v>
+      <c r="J4" s="4">
+        <v>285.44</v>
+      </c>
+      <c r="K4" s="4">
+        <v>410</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4" t="s">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
@@ -3605,11 +3622,15 @@
       <c r="CI4" s="4"/>
       <c r="CJ4" s="4"/>
       <c r="CK4" s="4"/>
-      <c r="CL4" s="4"/>
+      <c r="CL4" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM4" s="4"/>
       <c r="CN4" s="4"/>
       <c r="CO4" s="4"/>
-      <c r="CP4" s="4"/>
+      <c r="CP4" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ4" s="4"/>
       <c r="CR4" s="4"/>
       <c r="CS4" s="4"/>
@@ -3632,33 +3653,33 @@
         <v>456</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>92</v>
+        <v>306</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>78</v>
+      <c r="J5" s="4">
+        <v>276.88</v>
+      </c>
+      <c r="K5" s="4">
+        <v>410</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4" t="s">
-        <v>95</v>
+        <v>308</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
@@ -3782,11 +3803,15 @@
       <c r="CI5" s="4"/>
       <c r="CJ5" s="4"/>
       <c r="CK5" s="4"/>
-      <c r="CL5" s="4"/>
+      <c r="CL5" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM5" s="4"/>
       <c r="CN5" s="4"/>
       <c r="CO5" s="4"/>
-      <c r="CP5" s="4"/>
+      <c r="CP5" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ5" s="4"/>
       <c r="CR5" s="4"/>
       <c r="CS5" s="4"/>
@@ -3815,27 +3840,27 @@
         <v>458</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>78</v>
+      <c r="J6" s="4">
+        <v>240</v>
+      </c>
+      <c r="K6" s="4">
+        <v>405</v>
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
@@ -3986,33 +4011,33 @@
         <v>456</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>101</v>
+        <v>255</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>103</v>
+        <v>160</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>78</v>
+      <c r="J7" s="4">
+        <v>231</v>
+      </c>
+      <c r="K7" s="4">
+        <v>405</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -4163,33 +4188,33 @@
         <v>456</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>78</v>
+      <c r="J8" s="4">
+        <v>219</v>
+      </c>
+      <c r="K8" s="4">
+        <v>405</v>
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
-        <v>109</v>
+        <v>254</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
@@ -4346,27 +4371,27 @@
         <v>458</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>111</v>
+        <v>223</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>89</v>
+        <v>224</v>
       </c>
       <c r="I9" s="4"/>
-      <c r="J9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>78</v>
+      <c r="J9" s="4">
+        <v>202.52</v>
+      </c>
+      <c r="K9" s="4">
+        <v>405</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
-        <v>39</v>
+        <v>226</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -4517,33 +4542,33 @@
         <v>456</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>113</v>
+        <v>260</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>78</v>
+      <c r="J10" s="4">
+        <v>257.52</v>
+      </c>
+      <c r="K10" s="4">
+        <v>405</v>
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="4" t="s">
-        <v>115</v>
+        <v>259</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
@@ -4694,33 +4719,33 @@
         <v>456</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>116</v>
+        <v>279</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>118</v>
+        <v>280</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>89</v>
+        <v>224</v>
       </c>
       <c r="I11" s="4"/>
-      <c r="J11" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>78</v>
+      <c r="J11" s="4">
+        <v>313.52</v>
+      </c>
+      <c r="K11" s="4">
+        <v>405</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4" t="s">
-        <v>120</v>
+        <v>282</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
@@ -4877,27 +4902,27 @@
         <v>458</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I12" s="4"/>
-      <c r="J12" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>78</v>
+      <c r="J12" s="4">
+        <v>241</v>
+      </c>
+      <c r="K12" s="4">
+        <v>410</v>
       </c>
       <c r="L12" s="4"/>
       <c r="M12" s="4" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
@@ -5021,11 +5046,15 @@
       <c r="CI12" s="4"/>
       <c r="CJ12" s="4"/>
       <c r="CK12" s="4"/>
-      <c r="CL12" s="4"/>
+      <c r="CL12" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM12" s="4"/>
       <c r="CN12" s="4"/>
       <c r="CO12" s="4"/>
-      <c r="CP12" s="4"/>
+      <c r="CP12" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ12" s="4"/>
       <c r="CR12" s="4"/>
       <c r="CS12" s="4"/>
@@ -5066,11 +5095,11 @@
         <v>83</v>
       </c>
       <c r="I13" s="4"/>
-      <c r="J13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>78</v>
+      <c r="J13" s="4">
+        <v>271.52</v>
+      </c>
+      <c r="K13" s="4">
+        <v>405</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="4" t="s">
@@ -5231,27 +5260,27 @@
         <v>458</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>75</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>78</v>
+      <c r="J14" s="4">
+        <v>277</v>
+      </c>
+      <c r="K14" s="4">
+        <v>405</v>
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="4" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
@@ -5408,27 +5437,27 @@
         <v>458</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>135</v>
+        <v>98</v>
       </c>
       <c r="I15" s="4"/>
-      <c r="J15" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>78</v>
+      <c r="J15" s="4">
+        <v>234</v>
+      </c>
+      <c r="K15" s="4">
+        <v>405</v>
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="4" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
@@ -5579,33 +5608,33 @@
         <v>456</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>138</v>
+        <v>312</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>118</v>
+        <v>313</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="I16" s="4"/>
-      <c r="J16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>78</v>
+      <c r="J16" s="4">
+        <v>248.4</v>
+      </c>
+      <c r="K16" s="4">
+        <v>410</v>
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
@@ -5729,11 +5758,15 @@
       <c r="CI16" s="4"/>
       <c r="CJ16" s="4"/>
       <c r="CK16" s="4"/>
-      <c r="CL16" s="4"/>
+      <c r="CL16" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM16" s="4"/>
       <c r="CN16" s="4"/>
       <c r="CO16" s="4"/>
-      <c r="CP16" s="4"/>
+      <c r="CP16" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ16" s="4"/>
       <c r="CR16" s="4"/>
       <c r="CS16" s="4"/>
@@ -5762,27 +5795,27 @@
         <v>458</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>122</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="I17" s="4"/>
-      <c r="J17" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>78</v>
+      <c r="J17" s="4">
+        <v>249.52</v>
+      </c>
+      <c r="K17" s="4">
+        <v>405</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
@@ -5933,33 +5966,33 @@
         <v>456</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I18" s="4"/>
-      <c r="J18" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>78</v>
+      <c r="J18" s="4">
+        <v>230</v>
+      </c>
+      <c r="K18" s="4">
+        <v>405</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4" t="s">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -6110,33 +6143,33 @@
         <v>456</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>151</v>
+        <v>283</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="I19" s="4"/>
-      <c r="J19" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>78</v>
+      <c r="J19" s="4">
+        <v>253.52</v>
+      </c>
+      <c r="K19" s="4">
+        <v>405</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4" t="s">
-        <v>154</v>
+        <v>285</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -6305,11 +6338,11 @@
         <v>122</v>
       </c>
       <c r="I20" s="4"/>
-      <c r="J20" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>78</v>
+      <c r="J20" s="4">
+        <v>261.52</v>
+      </c>
+      <c r="K20" s="4">
+        <v>405</v>
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="4" t="s">
@@ -6470,27 +6503,27 @@
         <v>458</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="I21" s="4"/>
-      <c r="J21" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>163</v>
+      <c r="J21" s="4">
+        <v>231</v>
+      </c>
+      <c r="K21" s="4">
+        <v>405</v>
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -6614,15 +6647,11 @@
       <c r="CI21" s="4"/>
       <c r="CJ21" s="4"/>
       <c r="CK21" s="4"/>
-      <c r="CL21" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL21" s="4"/>
       <c r="CM21" s="4"/>
       <c r="CN21" s="4"/>
       <c r="CO21" s="4"/>
-      <c r="CP21" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP21" s="4"/>
       <c r="CQ21" s="4"/>
       <c r="CR21" s="4"/>
       <c r="CS21" s="4"/>
@@ -6651,27 +6680,27 @@
         <v>458</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I22" s="4"/>
-      <c r="J22" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>163</v>
+      <c r="J22" s="4">
+        <v>268.32</v>
+      </c>
+      <c r="K22" s="4">
+        <v>410</v>
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="4" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
@@ -6832,27 +6861,27 @@
         <v>458</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I23" s="4"/>
-      <c r="J23" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>163</v>
+      <c r="J23" s="4">
+        <v>234</v>
+      </c>
+      <c r="K23" s="4">
+        <v>405</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
@@ -6976,15 +7005,11 @@
       <c r="CI23" s="4"/>
       <c r="CJ23" s="4"/>
       <c r="CK23" s="4"/>
-      <c r="CL23" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL23" s="4"/>
       <c r="CM23" s="4"/>
       <c r="CN23" s="4"/>
       <c r="CO23" s="4"/>
-      <c r="CP23" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP23" s="4"/>
       <c r="CQ23" s="4"/>
       <c r="CR23" s="4"/>
       <c r="CS23" s="4"/>
@@ -7013,27 +7038,27 @@
         <v>458</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>143</v>
       </c>
       <c r="I24" s="4"/>
-      <c r="J24" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>163</v>
+      <c r="J24" s="4">
+        <v>272.83999999999997</v>
+      </c>
+      <c r="K24" s="4">
+        <v>410</v>
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="4" t="s">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
@@ -7194,27 +7219,27 @@
         <v>458</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>178</v>
+        <v>81</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="I25" s="4"/>
-      <c r="J25" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>163</v>
+      <c r="J25" s="4">
+        <v>246</v>
+      </c>
+      <c r="K25" s="4">
+        <v>405</v>
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="4" t="s">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
@@ -7338,15 +7363,11 @@
       <c r="CI25" s="4"/>
       <c r="CJ25" s="4"/>
       <c r="CK25" s="4"/>
-      <c r="CL25" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL25" s="4"/>
       <c r="CM25" s="4"/>
       <c r="CN25" s="4"/>
       <c r="CO25" s="4"/>
-      <c r="CP25" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP25" s="4"/>
       <c r="CQ25" s="4"/>
       <c r="CR25" s="4"/>
       <c r="CS25" s="4"/>
@@ -7369,33 +7390,33 @@
         <v>456</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>183</v>
+        <v>309</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>184</v>
+        <v>310</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>160</v>
+        <v>83</v>
       </c>
       <c r="I26" s="4"/>
-      <c r="J26" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>163</v>
+      <c r="J26" s="4">
+        <v>244.44</v>
+      </c>
+      <c r="K26" s="4">
+        <v>410</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="4" t="s">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
@@ -7550,33 +7571,33 @@
         <v>456</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="I27" s="4"/>
-      <c r="J27" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>163</v>
+      <c r="J27" s="4">
+        <v>243.52</v>
+      </c>
+      <c r="K27" s="4">
+        <v>405</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4" t="s">
-        <v>191</v>
+        <v>247</v>
       </c>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
@@ -7700,15 +7721,11 @@
       <c r="CI27" s="4"/>
       <c r="CJ27" s="4"/>
       <c r="CK27" s="4"/>
-      <c r="CL27" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL27" s="4"/>
       <c r="CM27" s="4"/>
       <c r="CN27" s="4"/>
       <c r="CO27" s="4"/>
-      <c r="CP27" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP27" s="4"/>
       <c r="CQ27" s="4"/>
       <c r="CR27" s="4"/>
       <c r="CS27" s="4"/>
@@ -7737,27 +7754,27 @@
         <v>458</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="I28" s="4"/>
-      <c r="J28" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>163</v>
+      <c r="J28" s="4">
+        <v>250.04</v>
+      </c>
+      <c r="K28" s="4">
+        <v>410</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
@@ -7912,33 +7929,33 @@
         <v>456</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>108</v>
+        <v>237</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>163</v>
+      <c r="J29" s="4">
+        <v>240</v>
+      </c>
+      <c r="K29" s="4">
+        <v>405</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4" t="s">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
@@ -8062,15 +8079,11 @@
       <c r="CI29" s="4"/>
       <c r="CJ29" s="4"/>
       <c r="CK29" s="4"/>
-      <c r="CL29" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL29" s="4"/>
       <c r="CM29" s="4"/>
       <c r="CN29" s="4"/>
       <c r="CO29" s="4"/>
-      <c r="CP29" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP29" s="4"/>
       <c r="CQ29" s="4"/>
       <c r="CR29" s="4"/>
       <c r="CS29" s="4"/>
@@ -8093,33 +8106,33 @@
         <v>456</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>147</v>
+        <v>269</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I30" s="4"/>
-      <c r="J30" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>163</v>
+      <c r="J30" s="4">
+        <v>255.52</v>
+      </c>
+      <c r="K30" s="4">
+        <v>405</v>
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="4" t="s">
-        <v>200</v>
+        <v>271</v>
       </c>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
@@ -8243,15 +8256,11 @@
       <c r="CI30" s="4"/>
       <c r="CJ30" s="4"/>
       <c r="CK30" s="4"/>
-      <c r="CL30" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL30" s="4"/>
       <c r="CM30" s="4"/>
       <c r="CN30" s="4"/>
       <c r="CO30" s="4"/>
-      <c r="CP30" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP30" s="4"/>
       <c r="CQ30" s="4"/>
       <c r="CR30" s="4"/>
       <c r="CS30" s="4"/>
@@ -8274,33 +8283,33 @@
         <v>456</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>174</v>
+        <v>276</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="I31" s="4"/>
-      <c r="J31" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>163</v>
+      <c r="J31" s="4">
+        <v>283</v>
+      </c>
+      <c r="K31" s="4">
+        <v>405</v>
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="4" t="s">
-        <v>203</v>
+        <v>278</v>
       </c>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
@@ -8424,15 +8433,11 @@
       <c r="CI31" s="4"/>
       <c r="CJ31" s="4"/>
       <c r="CK31" s="4"/>
-      <c r="CL31" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL31" s="4"/>
       <c r="CM31" s="4"/>
       <c r="CN31" s="4"/>
       <c r="CO31" s="4"/>
-      <c r="CP31" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP31" s="4"/>
       <c r="CQ31" s="4"/>
       <c r="CR31" s="4"/>
       <c r="CS31" s="4"/>
@@ -8455,33 +8460,33 @@
         <v>456</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>204</v>
+        <v>248</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="I32" s="4"/>
-      <c r="J32" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>163</v>
+      <c r="J32" s="4">
+        <v>254</v>
+      </c>
+      <c r="K32" s="4">
+        <v>405</v>
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
@@ -8605,15 +8610,11 @@
       <c r="CI32" s="4"/>
       <c r="CJ32" s="4"/>
       <c r="CK32" s="4"/>
-      <c r="CL32" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL32" s="4"/>
       <c r="CM32" s="4"/>
       <c r="CN32" s="4"/>
       <c r="CO32" s="4"/>
-      <c r="CP32" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP32" s="4"/>
       <c r="CQ32" s="4"/>
       <c r="CR32" s="4"/>
       <c r="CS32" s="4"/>
@@ -8636,33 +8637,33 @@
         <v>456</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="I33" s="4"/>
-      <c r="J33" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>163</v>
+      <c r="J33" s="4">
+        <v>211</v>
+      </c>
+      <c r="K33" s="4">
+        <v>405</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
@@ -8786,15 +8787,11 @@
       <c r="CI33" s="4"/>
       <c r="CJ33" s="4"/>
       <c r="CK33" s="4"/>
-      <c r="CL33" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL33" s="4"/>
       <c r="CM33" s="4"/>
       <c r="CN33" s="4"/>
       <c r="CO33" s="4"/>
-      <c r="CP33" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP33" s="4"/>
       <c r="CQ33" s="4"/>
       <c r="CR33" s="4"/>
       <c r="CS33" s="4"/>
@@ -8823,27 +8820,27 @@
         <v>458</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>210</v>
+        <v>146</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>211</v>
+        <v>147</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I34" s="4"/>
-      <c r="J34" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>163</v>
+      <c r="J34" s="4">
+        <v>253</v>
+      </c>
+      <c r="K34" s="4">
+        <v>405</v>
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="4" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
@@ -8967,15 +8964,11 @@
       <c r="CI34" s="4"/>
       <c r="CJ34" s="4"/>
       <c r="CK34" s="4"/>
-      <c r="CL34" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL34" s="4"/>
       <c r="CM34" s="4"/>
       <c r="CN34" s="4"/>
       <c r="CO34" s="4"/>
-      <c r="CP34" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP34" s="4"/>
       <c r="CQ34" s="4"/>
       <c r="CR34" s="4"/>
       <c r="CS34" s="4"/>
@@ -9004,27 +8997,27 @@
         <v>458</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="I35" s="4"/>
-      <c r="J35" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>163</v>
+      <c r="J35" s="4">
+        <v>254.52</v>
+      </c>
+      <c r="K35" s="4">
+        <v>410</v>
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="4" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
@@ -9185,27 +9178,27 @@
         <v>458</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="I36" s="4"/>
-      <c r="J36" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>163</v>
+      <c r="J36" s="4">
+        <v>260.56</v>
+      </c>
+      <c r="K36" s="4">
+        <v>410</v>
       </c>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
@@ -9360,33 +9353,33 @@
         <v>456</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="F37" s="4">
-        <v>6</v>
-      </c>
-      <c r="G37" s="4">
-        <v>5.3</v>
-      </c>
-      <c r="H37" s="4">
-        <v>9</v>
+        <v>315</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4">
-        <v>67.88</v>
+        <v>255.92</v>
       </c>
       <c r="K37" s="4">
-        <v>101.25</v>
+        <v>410</v>
       </c>
       <c r="L37" s="4"/>
-      <c r="M37" s="4">
-        <v>182</v>
+      <c r="M37" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
@@ -9510,11 +9503,15 @@
       <c r="CI37" s="4"/>
       <c r="CJ37" s="4"/>
       <c r="CK37" s="4"/>
-      <c r="CL37" s="4"/>
+      <c r="CL37" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM37" s="4"/>
       <c r="CN37" s="4"/>
       <c r="CO37" s="4"/>
-      <c r="CP37" s="4"/>
+      <c r="CP37" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ37" s="4"/>
       <c r="CR37" s="4"/>
       <c r="CS37" s="4"/>
@@ -9537,33 +9534,33 @@
         <v>456</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>222</v>
+        <v>286</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>223</v>
+        <v>287</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="I38" s="4"/>
-      <c r="J38" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>78</v>
+      <c r="J38" s="4">
+        <v>254.32</v>
+      </c>
+      <c r="K38" s="4">
+        <v>410</v>
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4" t="s">
-        <v>226</v>
+        <v>289</v>
       </c>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
@@ -9687,11 +9684,15 @@
       <c r="CI38" s="4"/>
       <c r="CJ38" s="4"/>
       <c r="CK38" s="4"/>
-      <c r="CL38" s="4"/>
+      <c r="CL38" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM38" s="4"/>
       <c r="CN38" s="4"/>
       <c r="CO38" s="4"/>
-      <c r="CP38" s="4"/>
+      <c r="CP38" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ38" s="4"/>
       <c r="CR38" s="4"/>
       <c r="CS38" s="4"/>
@@ -9714,33 +9715,33 @@
         <v>456</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>228</v>
+        <v>322</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>189</v>
       </c>
       <c r="I39" s="4"/>
-      <c r="J39" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>163</v>
+      <c r="J39" s="4">
+        <v>247.96</v>
+      </c>
+      <c r="K39" s="4">
+        <v>410</v>
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="4" t="s">
-        <v>230</v>
+        <v>325</v>
       </c>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
@@ -9864,11 +9865,15 @@
       <c r="CI39" s="4"/>
       <c r="CJ39" s="4"/>
       <c r="CK39" s="4"/>
-      <c r="CL39" s="4"/>
+      <c r="CL39" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM39" s="4"/>
       <c r="CN39" s="4"/>
       <c r="CO39" s="4"/>
-      <c r="CP39" s="4"/>
+      <c r="CP39" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ39" s="4"/>
       <c r="CR39" s="4"/>
       <c r="CS39" s="4"/>
@@ -9891,33 +9896,33 @@
         <v>456</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>232</v>
+        <v>92</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>233</v>
+        <v>93</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="I40" s="4"/>
-      <c r="J40" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>78</v>
+      <c r="J40" s="4">
+        <v>260.52</v>
+      </c>
+      <c r="K40" s="4">
+        <v>405</v>
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="4" t="s">
-        <v>235</v>
+        <v>95</v>
       </c>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
@@ -10074,27 +10079,27 @@
         <v>458</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>236</v>
+        <v>345</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>237</v>
+        <v>174</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="I41" s="4"/>
-      <c r="J41" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>78</v>
+      <c r="J41" s="4">
+        <v>265.52</v>
+      </c>
+      <c r="K41" s="4">
+        <v>405</v>
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="4" t="s">
-        <v>240</v>
+        <v>346</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
@@ -10251,27 +10256,27 @@
         <v>458</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>174</v>
+        <v>296</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="I42" s="4"/>
-      <c r="J42" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>78</v>
+      <c r="J42" s="4">
+        <v>255.6</v>
+      </c>
+      <c r="K42" s="4">
+        <v>410</v>
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="4" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
@@ -10395,11 +10400,15 @@
       <c r="CI42" s="4"/>
       <c r="CJ42" s="4"/>
       <c r="CK42" s="4"/>
-      <c r="CL42" s="4"/>
+      <c r="CL42" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM42" s="4"/>
       <c r="CN42" s="4"/>
       <c r="CO42" s="4"/>
-      <c r="CP42" s="4"/>
+      <c r="CP42" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ42" s="4"/>
       <c r="CR42" s="4"/>
       <c r="CS42" s="4"/>
@@ -10422,33 +10431,33 @@
         <v>456</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>245</v>
+        <v>173</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="I43" s="4"/>
-      <c r="J43" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>78</v>
+      <c r="J43" s="4">
+        <v>264.12</v>
+      </c>
+      <c r="K43" s="4">
+        <v>410</v>
       </c>
       <c r="L43" s="4"/>
       <c r="M43" s="4" t="s">
-        <v>247</v>
+        <v>176</v>
       </c>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
@@ -10572,11 +10581,15 @@
       <c r="CI43" s="4"/>
       <c r="CJ43" s="4"/>
       <c r="CK43" s="4"/>
-      <c r="CL43" s="4"/>
+      <c r="CL43" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM43" s="4"/>
       <c r="CN43" s="4"/>
       <c r="CO43" s="4"/>
-      <c r="CP43" s="4"/>
+      <c r="CP43" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ43" s="4"/>
       <c r="CR43" s="4"/>
       <c r="CS43" s="4"/>
@@ -10599,33 +10612,33 @@
         <v>456</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="I44" s="4"/>
-      <c r="J44" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>78</v>
+      <c r="J44" s="4">
+        <v>256.36</v>
+      </c>
+      <c r="K44" s="4">
+        <v>410</v>
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="4" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
@@ -10749,11 +10762,15 @@
       <c r="CI44" s="4"/>
       <c r="CJ44" s="4"/>
       <c r="CK44" s="4"/>
-      <c r="CL44" s="4"/>
+      <c r="CL44" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM44" s="4"/>
       <c r="CN44" s="4"/>
       <c r="CO44" s="4"/>
-      <c r="CP44" s="4"/>
+      <c r="CP44" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ44" s="4"/>
       <c r="CR44" s="4"/>
       <c r="CS44" s="4"/>
@@ -10782,27 +10799,27 @@
         <v>458</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="I45" s="4"/>
-      <c r="J45" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>78</v>
+      <c r="J45" s="4">
+        <v>249</v>
+      </c>
+      <c r="K45" s="4">
+        <v>405</v>
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="4" t="s">
-        <v>218</v>
+        <v>325</v>
       </c>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
@@ -10953,33 +10970,33 @@
         <v>456</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>252</v>
+        <v>151</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="I46" s="4"/>
-      <c r="J46" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>78</v>
+      <c r="J46" s="4">
+        <v>279</v>
+      </c>
+      <c r="K46" s="4">
+        <v>405</v>
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="4" t="s">
-        <v>254</v>
+        <v>154</v>
       </c>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
@@ -11136,27 +11153,27 @@
         <v>458</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>255</v>
+        <v>338</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>256</v>
+        <v>339</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="I47" s="4"/>
-      <c r="J47" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>78</v>
+      <c r="J47" s="4">
+        <v>394</v>
+      </c>
+      <c r="K47" s="4">
+        <v>405</v>
       </c>
       <c r="L47" s="4"/>
       <c r="M47" s="4" t="s">
-        <v>100</v>
+        <v>342</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
@@ -11172,7 +11189,9 @@
       <c r="Y47" s="4"/>
       <c r="Z47" s="4"/>
       <c r="AA47" s="4"/>
-      <c r="AB47" s="4"/>
+      <c r="AB47" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="AC47" s="4" t="s">
         <v>459</v>
       </c>
@@ -11296,7 +11315,9 @@
       <c r="CY47" s="4"/>
       <c r="CZ47" s="4"/>
       <c r="DA47" s="4"/>
-      <c r="DB47" s="4"/>
+      <c r="DB47" s="4" t="s">
+        <v>461</v>
+      </c>
       <c r="DC47" s="4"/>
     </row>
     <row r="48" spans="1:107" x14ac:dyDescent="0.4">
@@ -11313,27 +11334,27 @@
         <v>458</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="I48" s="4"/>
-      <c r="J48" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>78</v>
+      <c r="J48" s="4">
+        <v>281.52</v>
+      </c>
+      <c r="K48" s="4">
+        <v>405</v>
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="4" t="s">
-        <v>259</v>
+        <v>154</v>
       </c>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
@@ -11484,33 +11505,33 @@
         <v>456</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>260</v>
+        <v>116</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>237</v>
+        <v>118</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>262</v>
+        <v>89</v>
       </c>
       <c r="I49" s="4"/>
-      <c r="J49" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>78</v>
+      <c r="J49" s="4">
+        <v>265.52</v>
+      </c>
+      <c r="K49" s="4">
+        <v>405</v>
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="4" t="s">
-        <v>259</v>
+        <v>120</v>
       </c>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
@@ -11667,27 +11688,27 @@
         <v>458</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>111</v>
+        <v>237</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>143</v>
+        <v>238</v>
       </c>
       <c r="I50" s="4"/>
-      <c r="J50" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>78</v>
+      <c r="J50" s="4">
+        <v>231.52</v>
+      </c>
+      <c r="K50" s="4">
+        <v>405</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4" t="s">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
@@ -11838,33 +11859,33 @@
         <v>456</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>265</v>
+        <v>113</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>266</v>
+        <v>75</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="I51" s="4"/>
-      <c r="J51" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>78</v>
+      <c r="J51" s="4">
+        <v>235.52</v>
+      </c>
+      <c r="K51" s="4">
+        <v>405</v>
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="4" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
@@ -12021,27 +12042,27 @@
         <v>458</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>170</v>
+        <v>42</v>
       </c>
       <c r="I52" s="4"/>
-      <c r="J52" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>78</v>
+      <c r="J52" s="4">
+        <v>399</v>
+      </c>
+      <c r="K52" s="4">
+        <v>405</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
@@ -12057,7 +12078,9 @@
       <c r="Y52" s="4"/>
       <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
+      <c r="AB52" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="AC52" s="4" t="s">
         <v>459</v>
       </c>
@@ -12181,7 +12204,9 @@
       <c r="CY52" s="4"/>
       <c r="CZ52" s="4"/>
       <c r="DA52" s="4"/>
-      <c r="DB52" s="4"/>
+      <c r="DB52" s="4" t="s">
+        <v>461</v>
+      </c>
       <c r="DC52" s="4"/>
     </row>
     <row r="53" spans="1:107" x14ac:dyDescent="0.4">
@@ -12198,27 +12223,27 @@
         <v>458</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I53" s="4"/>
-      <c r="J53" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>78</v>
+      <c r="J53" s="4">
+        <v>250.28</v>
+      </c>
+      <c r="K53" s="4">
+        <v>410</v>
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="4" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
@@ -12342,11 +12367,15 @@
       <c r="CI53" s="4"/>
       <c r="CJ53" s="4"/>
       <c r="CK53" s="4"/>
-      <c r="CL53" s="4"/>
+      <c r="CL53" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM53" s="4"/>
       <c r="CN53" s="4"/>
       <c r="CO53" s="4"/>
-      <c r="CP53" s="4"/>
+      <c r="CP53" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ53" s="4"/>
       <c r="CR53" s="4"/>
       <c r="CS53" s="4"/>
@@ -12369,33 +12398,33 @@
         <v>456</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>276</v>
+        <v>88</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I54" s="4"/>
-      <c r="J54" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>78</v>
+      <c r="J54" s="4">
+        <v>254</v>
+      </c>
+      <c r="K54" s="4">
+        <v>405</v>
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="4" t="s">
-        <v>278</v>
+        <v>91</v>
       </c>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
@@ -12552,27 +12581,27 @@
         <v>458</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>280</v>
+        <v>319</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="I55" s="4"/>
-      <c r="J55" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>78</v>
+      <c r="J55" s="4">
+        <v>250</v>
+      </c>
+      <c r="K55" s="4">
+        <v>410</v>
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="4" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
@@ -12696,11 +12725,15 @@
       <c r="CI55" s="4"/>
       <c r="CJ55" s="4"/>
       <c r="CK55" s="4"/>
-      <c r="CL55" s="4"/>
+      <c r="CL55" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM55" s="4"/>
       <c r="CN55" s="4"/>
       <c r="CO55" s="4"/>
-      <c r="CP55" s="4"/>
+      <c r="CP55" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ55" s="4"/>
       <c r="CR55" s="4"/>
       <c r="CS55" s="4"/>
@@ -12723,33 +12756,33 @@
         <v>456</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="I56" s="4"/>
-      <c r="J56" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>78</v>
+      <c r="J56" s="4">
+        <v>261.52</v>
+      </c>
+      <c r="K56" s="4">
+        <v>410</v>
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="4" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
@@ -12900,33 +12933,33 @@
         <v>456</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>286</v>
+        <v>187</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>83</v>
+        <v>152</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>287</v>
+        <v>188</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="I57" s="4"/>
-      <c r="J57" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>163</v>
+      <c r="J57" s="4">
+        <v>223.32</v>
+      </c>
+      <c r="K57" s="4">
+        <v>410</v>
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="4" t="s">
-        <v>289</v>
+        <v>191</v>
       </c>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
@@ -13087,27 +13120,27 @@
         <v>458</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>292</v>
+        <v>178</v>
       </c>
       <c r="I58" s="4"/>
-      <c r="J58" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>163</v>
+      <c r="J58" s="4">
+        <v>273.12</v>
+      </c>
+      <c r="K58" s="4">
+        <v>410</v>
       </c>
       <c r="L58" s="4"/>
       <c r="M58" s="4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
@@ -13268,27 +13301,27 @@
         <v>458</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>296</v>
+        <v>111</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="I59" s="4"/>
-      <c r="J59" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>163</v>
+      <c r="J59" s="4">
+        <v>269</v>
+      </c>
+      <c r="K59" s="4">
+        <v>405</v>
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="4" t="s">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
@@ -13412,15 +13445,11 @@
       <c r="CI59" s="4"/>
       <c r="CJ59" s="4"/>
       <c r="CK59" s="4"/>
-      <c r="CL59" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL59" s="4"/>
       <c r="CM59" s="4"/>
       <c r="CN59" s="4"/>
       <c r="CO59" s="4"/>
-      <c r="CP59" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP59" s="4"/>
       <c r="CQ59" s="4"/>
       <c r="CR59" s="4"/>
       <c r="CS59" s="4"/>
@@ -13449,27 +13478,27 @@
         <v>458</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>299</v>
+        <v>174</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="I60" s="4"/>
-      <c r="J60" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>163</v>
+      <c r="J60" s="4">
+        <v>248.52</v>
+      </c>
+      <c r="K60" s="4">
+        <v>405</v>
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="4" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
@@ -13593,15 +13622,11 @@
       <c r="CI60" s="4"/>
       <c r="CJ60" s="4"/>
       <c r="CK60" s="4"/>
-      <c r="CL60" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL60" s="4"/>
       <c r="CM60" s="4"/>
       <c r="CN60" s="4"/>
       <c r="CO60" s="4"/>
-      <c r="CP60" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP60" s="4"/>
       <c r="CQ60" s="4"/>
       <c r="CR60" s="4"/>
       <c r="CS60" s="4"/>
@@ -13624,33 +13649,33 @@
         <v>456</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>302</v>
+        <v>101</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>303</v>
+        <v>102</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="I61" s="4"/>
-      <c r="J61" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>163</v>
+      <c r="J61" s="4">
+        <v>263</v>
+      </c>
+      <c r="K61" s="4">
+        <v>405</v>
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="4" t="s">
-        <v>305</v>
+        <v>105</v>
       </c>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
@@ -13774,15 +13799,11 @@
       <c r="CI61" s="4"/>
       <c r="CJ61" s="4"/>
       <c r="CK61" s="4"/>
-      <c r="CL61" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL61" s="4"/>
       <c r="CM61" s="4"/>
       <c r="CN61" s="4"/>
       <c r="CO61" s="4"/>
-      <c r="CP61" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP61" s="4"/>
       <c r="CQ61" s="4"/>
       <c r="CR61" s="4"/>
       <c r="CS61" s="4"/>
@@ -13805,33 +13826,33 @@
         <v>456</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="I62" s="4"/>
-      <c r="J62" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>163</v>
+      <c r="J62" s="4">
+        <v>274</v>
+      </c>
+      <c r="K62" s="4">
+        <v>410</v>
       </c>
       <c r="L62" s="4"/>
       <c r="M62" s="4" t="s">
-        <v>308</v>
+        <v>195</v>
       </c>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
@@ -13986,33 +14007,33 @@
         <v>456</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>309</v>
+        <v>177</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>310</v>
+        <v>179</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="I63" s="4"/>
-      <c r="J63" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>163</v>
+      <c r="J63" s="4">
+        <v>255</v>
+      </c>
+      <c r="K63" s="4">
+        <v>410</v>
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="4" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
@@ -14167,33 +14188,33 @@
         <v>456</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>312</v>
+        <v>159</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>313</v>
+        <v>118</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="I64" s="4"/>
-      <c r="J64" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>163</v>
+      <c r="J64" s="4">
+        <v>242</v>
+      </c>
+      <c r="K64" s="4">
+        <v>410</v>
       </c>
       <c r="L64" s="4"/>
       <c r="M64" s="4" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
@@ -14348,33 +14369,33 @@
         <v>456</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="H65" s="4" t="s">
-        <v>76</v>
+        <v>347</v>
+      </c>
+      <c r="F65" s="4">
+        <v>6</v>
+      </c>
+      <c r="G65" s="4">
+        <v>5.3</v>
+      </c>
+      <c r="H65" s="4">
+        <v>9</v>
       </c>
       <c r="I65" s="4"/>
-      <c r="J65" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>163</v>
+      <c r="J65" s="4">
+        <v>271.52</v>
+      </c>
+      <c r="K65" s="4">
+        <v>405</v>
       </c>
       <c r="L65" s="4"/>
-      <c r="M65" s="4" t="s">
-        <v>250</v>
+      <c r="M65" s="4">
+        <v>182</v>
       </c>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
@@ -14498,15 +14519,11 @@
       <c r="CI65" s="4"/>
       <c r="CJ65" s="4"/>
       <c r="CK65" s="4"/>
-      <c r="CL65" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL65" s="4"/>
       <c r="CM65" s="4"/>
       <c r="CN65" s="4"/>
       <c r="CO65" s="4"/>
-      <c r="CP65" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP65" s="4"/>
       <c r="CQ65" s="4"/>
       <c r="CR65" s="4"/>
       <c r="CS65" s="4"/>
@@ -14523,39 +14540,39 @@
     </row>
     <row r="66" spans="1:107" x14ac:dyDescent="0.4">
       <c r="A66" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>318</v>
+        <v>73</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>319</v>
+        <v>75</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>207</v>
+        <v>76</v>
       </c>
       <c r="I66" s="4"/>
-      <c r="J66" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>163</v>
+      <c r="J66" s="4">
+        <v>269.52</v>
+      </c>
+      <c r="K66" s="4">
+        <v>405</v>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4" t="s">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
@@ -14679,15 +14696,11 @@
       <c r="CI66" s="4"/>
       <c r="CJ66" s="4"/>
       <c r="CK66" s="4"/>
-      <c r="CL66" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL66" s="4"/>
       <c r="CM66" s="4"/>
       <c r="CN66" s="4"/>
       <c r="CO66" s="4"/>
-      <c r="CP66" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP66" s="4"/>
       <c r="CQ66" s="4"/>
       <c r="CR66" s="4"/>
       <c r="CS66" s="4"/>
@@ -14710,33 +14723,33 @@
         <v>456</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>322</v>
+        <v>110</v>
       </c>
       <c r="F67" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H67" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>189</v>
-      </c>
       <c r="I67" s="4"/>
-      <c r="J67" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>163</v>
+      <c r="J67" s="4">
+        <v>179.52</v>
+      </c>
+      <c r="K67" s="4">
+        <v>405</v>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4" t="s">
-        <v>325</v>
+        <v>39</v>
       </c>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
@@ -14860,15 +14873,11 @@
       <c r="CI67" s="4"/>
       <c r="CJ67" s="4"/>
       <c r="CK67" s="4"/>
-      <c r="CL67" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL67" s="4"/>
       <c r="CM67" s="4"/>
       <c r="CN67" s="4"/>
       <c r="CO67" s="4"/>
-      <c r="CP67" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP67" s="4"/>
       <c r="CQ67" s="4"/>
       <c r="CR67" s="4"/>
       <c r="CS67" s="4"/>
@@ -14891,33 +14900,33 @@
         <v>456</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>326</v>
+        <v>138</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>327</v>
+        <v>118</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="I68" s="4"/>
-      <c r="J68" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>163</v>
+      <c r="J68" s="4">
+        <v>239</v>
+      </c>
+      <c r="K68" s="4">
+        <v>405</v>
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
@@ -15041,15 +15050,11 @@
       <c r="CI68" s="4"/>
       <c r="CJ68" s="4"/>
       <c r="CK68" s="4"/>
-      <c r="CL68" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="CL68" s="4"/>
       <c r="CM68" s="4"/>
       <c r="CN68" s="4"/>
       <c r="CO68" s="4"/>
-      <c r="CP68" s="4">
-        <v>0.05</v>
-      </c>
+      <c r="CP68" s="4"/>
       <c r="CQ68" s="4"/>
       <c r="CR68" s="4"/>
       <c r="CS68" s="4"/>
@@ -15072,33 +15077,33 @@
         <v>456</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>329</v>
+        <v>219</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>330</v>
+        <v>215</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="I69" s="4"/>
-      <c r="J69" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>78</v>
+      <c r="J69" s="4">
+        <v>306.24</v>
+      </c>
+      <c r="K69" s="4">
+        <v>410</v>
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="4" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
@@ -15114,9 +15119,7 @@
       <c r="Y69" s="4"/>
       <c r="Z69" s="4"/>
       <c r="AA69" s="4"/>
-      <c r="AB69" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="AB69" s="4"/>
       <c r="AC69" s="4" t="s">
         <v>459</v>
       </c>
@@ -15224,11 +15227,15 @@
       <c r="CI69" s="4"/>
       <c r="CJ69" s="4"/>
       <c r="CK69" s="4"/>
-      <c r="CL69" s="4"/>
+      <c r="CL69" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM69" s="4"/>
       <c r="CN69" s="4"/>
       <c r="CO69" s="4"/>
-      <c r="CP69" s="4"/>
+      <c r="CP69" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ69" s="4"/>
       <c r="CR69" s="4"/>
       <c r="CS69" s="4"/>
@@ -15240,9 +15247,7 @@
       <c r="CY69" s="4"/>
       <c r="CZ69" s="4"/>
       <c r="DA69" s="4"/>
-      <c r="DB69" s="4" t="s">
-        <v>461</v>
-      </c>
+      <c r="DB69" s="4"/>
       <c r="DC69" s="4"/>
     </row>
     <row r="70" spans="1:107" x14ac:dyDescent="0.4">
@@ -15253,33 +15258,33 @@
         <v>456</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>333</v>
+        <v>204</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>334</v>
+        <v>188</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>335</v>
+        <v>166</v>
       </c>
       <c r="I70" s="4"/>
-      <c r="J70" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>163</v>
+      <c r="J70" s="4">
+        <v>269</v>
+      </c>
+      <c r="K70" s="4">
+        <v>410</v>
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="4" t="s">
-        <v>337</v>
+        <v>120</v>
       </c>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
@@ -15440,27 +15445,27 @@
         <v>458</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="I71" s="4"/>
-      <c r="J71" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>78</v>
+      <c r="J71" s="4">
+        <v>243.92</v>
+      </c>
+      <c r="K71" s="4">
+        <v>410</v>
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
@@ -15476,9 +15481,7 @@
       <c r="Y71" s="4"/>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
-      <c r="AB71" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="AB71" s="4"/>
       <c r="AC71" s="4" t="s">
         <v>459</v>
       </c>
@@ -15586,11 +15589,15 @@
       <c r="CI71" s="4"/>
       <c r="CJ71" s="4"/>
       <c r="CK71" s="4"/>
-      <c r="CL71" s="4"/>
+      <c r="CL71" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM71" s="4"/>
       <c r="CN71" s="4"/>
       <c r="CO71" s="4"/>
-      <c r="CP71" s="4"/>
+      <c r="CP71" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ71" s="4"/>
       <c r="CR71" s="4"/>
       <c r="CS71" s="4"/>
@@ -15602,9 +15609,7 @@
       <c r="CY71" s="4"/>
       <c r="CZ71" s="4"/>
       <c r="DA71" s="4"/>
-      <c r="DB71" s="4" t="s">
-        <v>461</v>
-      </c>
+      <c r="DB71" s="4"/>
       <c r="DC71" s="4"/>
     </row>
     <row r="72" spans="1:107" x14ac:dyDescent="0.4">
@@ -15615,33 +15620,33 @@
         <v>456</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>458</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="I72" s="4"/>
-      <c r="J72" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>78</v>
+      <c r="J72" s="4">
+        <v>251.44</v>
+      </c>
+      <c r="K72" s="4">
+        <v>410</v>
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="4" t="s">
-        <v>325</v>
+        <v>218</v>
       </c>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
@@ -15765,11 +15770,15 @@
       <c r="CI72" s="4"/>
       <c r="CJ72" s="4"/>
       <c r="CK72" s="4"/>
-      <c r="CL72" s="4"/>
+      <c r="CL72" s="4" t="s">
+        <v>460</v>
+      </c>
       <c r="CM72" s="4"/>
       <c r="CN72" s="4"/>
       <c r="CO72" s="4"/>
-      <c r="CP72" s="4"/>
+      <c r="CP72" s="4">
+        <v>0.05</v>
+      </c>
       <c r="CQ72" s="4"/>
       <c r="CR72" s="4"/>
       <c r="CS72" s="4"/>
@@ -15798,27 +15807,27 @@
         <v>458</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>345</v>
+        <v>257</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>174</v>
+        <v>256</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>81</v>
+        <v>216</v>
       </c>
       <c r="I73" s="4"/>
-      <c r="J73" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>78</v>
+      <c r="J73" s="4">
+        <v>259.52</v>
+      </c>
+      <c r="K73" s="4">
+        <v>405</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4" t="s">
-        <v>346</v>
+        <v>259</v>
       </c>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
@@ -15962,6 +15971,9 @@
       <c r="DC73" s="4"/>
     </row>
   </sheetData>
+  <sortState ref="A2:DC73">
+    <sortCondition ref="E2:E73"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15970,6 +15982,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -15994,6 +16007,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -16094,6 +16108,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -16115,6 +16130,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -16131,6 +16147,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -16209,6 +16226,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -16283,6 +16301,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -16317,6 +16336,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
